--- a/data/napoli/Servis_Durumu.xlsx
+++ b/data/napoli/Servis_Durumu.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,8 +56,12 @@
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -130,6 +134,12 @@
         <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -164,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -213,6 +223,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -579,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU12"/>
+  <dimension ref="A1:AV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="4"/>
@@ -592,232 +605,237 @@
           <t>Tramvay</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>2026-04-07</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>2026-04-05</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>2026-04-04</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>2026-03-28</t>
         </is>
       </c>
-      <c r="O1" s="5" t="inlineStr">
+      <c r="P1" s="5" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="P1" s="5" t="inlineStr">
+      <c r="Q1" s="5" t="inlineStr">
         <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="Q1" s="5" t="inlineStr">
+      <c r="R1" s="5" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="R1" s="5" t="inlineStr">
+      <c r="S1" s="5" t="inlineStr">
         <is>
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="S1" s="5" t="inlineStr">
+      <c r="T1" s="5" t="inlineStr">
         <is>
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="T1" s="5" t="inlineStr">
+      <c r="U1" s="5" t="inlineStr">
         <is>
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="U1" s="5" t="inlineStr">
+      <c r="V1" s="5" t="inlineStr">
         <is>
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="V1" s="5" t="inlineStr">
+      <c r="W1" s="5" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="W1" s="5" t="inlineStr">
+      <c r="X1" s="5" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="X1" s="5" t="inlineStr">
+      <c r="Y1" s="5" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="Y1" s="5" t="inlineStr">
+      <c r="Z1" s="5" t="inlineStr">
         <is>
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="Z1" s="5" t="inlineStr">
+      <c r="AA1" s="5" t="inlineStr">
         <is>
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AA1" s="5" t="inlineStr">
+      <c r="AB1" s="5" t="inlineStr">
         <is>
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="AB1" s="5" t="inlineStr">
+      <c r="AC1" s="5" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC1" s="5" t="inlineStr">
+      <c r="AD1" s="5" t="inlineStr">
         <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="AD1" s="5" t="inlineStr">
+      <c r="AE1" s="5" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AE1" s="5" t="inlineStr">
+      <c r="AF1" s="5" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="AF1" s="5" t="inlineStr">
+      <c r="AG1" s="5" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="AG1" s="5" t="inlineStr">
+      <c r="AH1" s="5" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="AH1" s="5" t="inlineStr">
+      <c r="AI1" s="5" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="AI1" s="5" t="inlineStr">
+      <c r="AJ1" s="5" t="inlineStr">
         <is>
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="AJ1" s="5" t="inlineStr">
+      <c r="AK1" s="5" t="inlineStr">
         <is>
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AK1" s="5" t="inlineStr">
+      <c r="AL1" s="5" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="AL1" s="5" t="inlineStr">
+      <c r="AM1" s="5" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="AM1" s="5" t="inlineStr">
+      <c r="AN1" s="5" t="inlineStr">
         <is>
           <t>2026-03-03</t>
         </is>
       </c>
-      <c r="AN1" s="5" t="inlineStr">
+      <c r="AO1" s="5" t="inlineStr">
         <is>
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="AO1" s="5" t="inlineStr">
+      <c r="AP1" s="5" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AP1" s="5" t="inlineStr">
+      <c r="AQ1" s="5" t="inlineStr">
         <is>
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AQ1" s="5" t="inlineStr">
+      <c r="AR1" s="5" t="inlineStr">
         <is>
           <t>2026-02-27</t>
         </is>
       </c>
-      <c r="AR1" s="5" t="inlineStr">
+      <c r="AS1" s="5" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="AS1" s="5" t="inlineStr">
+      <c r="AT1" s="5" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="AT1" s="5" t="inlineStr">
+      <c r="AU1" s="5" t="inlineStr">
         <is>
           <t>2026-02-24</t>
         </is>
       </c>
-      <c r="AU1" s="6" t="n"/>
+      <c r="AV1" s="6" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -825,7 +843,7 @@
           <t>1001</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -840,22 +858,26 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>✗</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
         <is>
           <t>✗</t>
         </is>
       </c>
-      <c r="H2" s="15" t="n"/>
       <c r="I2" s="15" t="n"/>
       <c r="J2" s="15" t="n"/>
       <c r="K2" s="15" t="n"/>
@@ -895,6 +917,7 @@
       <c r="AS2" s="15" t="n"/>
       <c r="AT2" s="15" t="n"/>
       <c r="AU2" s="15" t="n"/>
+      <c r="AV2" s="15" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -902,42 +925,46 @@
           <t>1002</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>⚠</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>⚠</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G3" s="17" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t>⚠</t>
         </is>
       </c>
-      <c r="H3" s="18" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I3" s="15" t="n"/>
+      <c r="I3" s="18" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J3" s="15" t="n"/>
       <c r="K3" s="15" t="n"/>
       <c r="L3" s="15" t="n"/>
@@ -976,6 +1003,7 @@
       <c r="AS3" s="15" t="n"/>
       <c r="AT3" s="15" t="n"/>
       <c r="AU3" s="15" t="n"/>
+      <c r="AV3" s="15" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -983,7 +1011,7 @@
           <t>1003</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -998,17 +1026,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>✗</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G4" s="18" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1018,7 +1046,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I4" s="15" t="n"/>
+      <c r="I4" s="18" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J4" s="15" t="n"/>
       <c r="K4" s="15" t="n"/>
       <c r="L4" s="15" t="n"/>
@@ -1057,6 +1089,7 @@
       <c r="AS4" s="15" t="n"/>
       <c r="AT4" s="15" t="n"/>
       <c r="AU4" s="15" t="n"/>
+      <c r="AV4" s="15" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -1064,7 +1097,7 @@
           <t>1004</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1079,13 +1112,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E5" s="15" t="n"/>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G5" s="18" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="n"/>
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1095,7 +1128,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I5" s="15" t="n"/>
+      <c r="I5" s="18" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J5" s="15" t="n"/>
       <c r="K5" s="15" t="n"/>
       <c r="L5" s="15" t="n"/>
@@ -1134,6 +1171,7 @@
       <c r="AS5" s="15" t="n"/>
       <c r="AT5" s="15" t="n"/>
       <c r="AU5" s="15" t="n"/>
+      <c r="AV5" s="15" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -1141,7 +1179,7 @@
           <t>1005</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1156,13 +1194,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E6" s="15" t="n"/>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G6" s="18" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1172,7 +1210,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I6" s="15" t="n"/>
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J6" s="15" t="n"/>
       <c r="K6" s="15" t="n"/>
       <c r="L6" s="15" t="n"/>
@@ -1211,6 +1253,7 @@
       <c r="AS6" s="15" t="n"/>
       <c r="AT6" s="15" t="n"/>
       <c r="AU6" s="15" t="n"/>
+      <c r="AV6" s="15" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -1218,7 +1261,7 @@
           <t>1006</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1233,18 +1276,22 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E7" s="15" t="n"/>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H7" s="15" t="n"/>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I7" s="15" t="n"/>
       <c r="J7" s="15" t="n"/>
       <c r="K7" s="15" t="n"/>
@@ -1284,6 +1331,7 @@
       <c r="AS7" s="15" t="n"/>
       <c r="AT7" s="15" t="n"/>
       <c r="AU7" s="15" t="n"/>
+      <c r="AV7" s="15" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1291,7 +1339,7 @@
           <t>1007</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1306,18 +1354,22 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E8" s="15" t="n"/>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H8" s="15" t="n"/>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I8" s="15" t="n"/>
       <c r="J8" s="15" t="n"/>
       <c r="K8" s="15" t="n"/>
@@ -1357,6 +1409,7 @@
       <c r="AS8" s="15" t="n"/>
       <c r="AT8" s="15" t="n"/>
       <c r="AU8" s="15" t="n"/>
+      <c r="AV8" s="15" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -1364,7 +1417,7 @@
           <t>1008</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1379,18 +1432,22 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E9" s="15" t="n"/>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H9" s="15" t="n"/>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="n"/>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I9" s="15" t="n"/>
       <c r="J9" s="15" t="n"/>
       <c r="K9" s="15" t="n"/>
@@ -1430,6 +1487,7 @@
       <c r="AS9" s="15" t="n"/>
       <c r="AT9" s="15" t="n"/>
       <c r="AU9" s="15" t="n"/>
+      <c r="AV9" s="15" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1437,7 +1495,7 @@
           <t>1009</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1452,18 +1510,22 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H10" s="15" t="n"/>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I10" s="15" t="n"/>
       <c r="J10" s="15" t="n"/>
       <c r="K10" s="15" t="n"/>
@@ -1503,6 +1565,7 @@
       <c r="AS10" s="15" t="n"/>
       <c r="AT10" s="15" t="n"/>
       <c r="AU10" s="15" t="n"/>
+      <c r="AV10" s="15" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -1510,7 +1573,7 @@
           <t>1010</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1525,18 +1588,22 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H11" s="15" t="n"/>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I11" s="15" t="n"/>
       <c r="J11" s="15" t="n"/>
       <c r="K11" s="15" t="n"/>
@@ -1576,6 +1643,7 @@
       <c r="AS11" s="15" t="n"/>
       <c r="AT11" s="15" t="n"/>
       <c r="AU11" s="15" t="n"/>
+      <c r="AV11" s="15" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="15" t="n"/>
@@ -1583,8 +1651,8 @@
       <c r="C12" s="15" t="n"/>
       <c r="D12" s="15" t="n"/>
       <c r="E12" s="15" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="7" t="n"/>
       <c r="H12" s="15" t="n"/>
       <c r="I12" s="15" t="n"/>
       <c r="J12" s="15" t="n"/>
@@ -1625,6 +1693,7 @@
       <c r="AS12" s="15" t="n"/>
       <c r="AT12" s="15" t="n"/>
       <c r="AU12" s="15" t="n"/>
+      <c r="AV12" s="15" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
